--- a/age_distribution_tidy.xlsx
+++ b/age_distribution_tidy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/med mini project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CE5358A-9DD3-4435-A49F-073DC7751DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{8CE5358A-9DD3-4435-A49F-073DC7751DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB65F81-F5C5-4992-9078-2D46B7DAA520}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{36764642-B66D-4662-97D4-AD47A217EAF5}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{36764642-B66D-4662-97D4-AD47A217EAF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <author>ABS</author>
   </authors>
   <commentList>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{846D1310-E83D-4ADD-ACE4-2CCD034439A7}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{846D1310-E83D-4ADD-ACE4-2CCD034439A7}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>0–4</t>
   </si>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>Northern Territory</t>
-  </si>
-  <si>
-    <t>Australian Capital Territory</t>
   </si>
   <si>
     <t>Australia</t>
@@ -222,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -230,7 +227,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -553,734 +549,659 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F791B93-A272-4460-B77A-39D571EEC61D}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" customWidth="1"/>
-    <col min="9" max="9" width="18.21875" customWidth="1"/>
-    <col min="10" max="10" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="9" max="9" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2">
+        <v>1510090</v>
+      </c>
+      <c r="C2" s="2">
         <v>475888</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
         <v>387304</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>309013</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>96822</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>168628</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>28669</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>17434</v>
       </c>
-      <c r="I2" s="2">
-        <v>26149</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1510090</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2">
+        <v>1610542</v>
+      </c>
+      <c r="C3" s="2">
         <v>498965</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>410490</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>333435</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>104468</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>185718</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>30935</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>18086</v>
       </c>
-      <c r="I3" s="2">
-        <v>28170</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1610542</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2">
+        <v>1674276</v>
+      </c>
+      <c r="C4" s="2">
         <v>520213</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>416608</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>359697</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>110329</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>187472</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>33140</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>17682</v>
       </c>
-      <c r="I4" s="2">
-        <v>28836</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1674276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2">
+        <v>1661944</v>
+      </c>
+      <c r="C5" s="2">
         <v>515115</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
         <v>414437</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>360520</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>111318</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>181791</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>33927</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>15916</v>
       </c>
-      <c r="I5" s="2">
-        <v>28639</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1661944</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2">
+        <v>1788041</v>
+      </c>
+      <c r="C6" s="2">
         <v>564670</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>468193</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>363528</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>116912</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>186828</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>29357</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>18555</v>
       </c>
-      <c r="I6" s="2">
-        <v>39804</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1788041</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2">
+        <v>1993635</v>
+      </c>
+      <c r="C7" s="2">
         <v>621039</v>
       </c>
-      <c r="C7" s="2">
+      <c r="D7" s="2">
         <v>525594</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>393565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>130325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>220174</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>37171</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>23913</v>
       </c>
-      <c r="I7" s="2">
-        <v>41569</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1993635</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2">
+        <v>2037179</v>
+      </c>
+      <c r="C8" s="2">
         <v>628957</v>
       </c>
-      <c r="C8" s="2">
+      <c r="D8" s="2">
         <v>543669</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>398085</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="2">
         <v>131046</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>226294</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <v>40885</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>25539</v>
       </c>
-      <c r="I8" s="2">
-        <v>42386</v>
-      </c>
-      <c r="J8" s="2">
-        <v>2037179</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2">
+        <v>1984476</v>
+      </c>
+      <c r="C9" s="2">
         <v>609962</v>
       </c>
-      <c r="C9" s="2">
+      <c r="D9" s="2">
         <v>531853</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>387426</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>128105</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>228824</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="2">
         <v>37217</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>22397</v>
       </c>
-      <c r="I9" s="2">
-        <v>38358</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1984476</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2">
+        <v>1851264</v>
+      </c>
+      <c r="C10" s="2">
         <v>573179</v>
       </c>
-      <c r="C10" s="2">
+      <c r="D10" s="2">
         <v>483790</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>373451</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="2">
         <v>120371</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <v>211251</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <v>34250</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>18994</v>
       </c>
-      <c r="I10" s="2">
-        <v>35627</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1851264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2">
+        <v>1628162</v>
+      </c>
+      <c r="C11" s="2">
         <v>505631</v>
       </c>
-      <c r="C11" s="2">
+      <c r="D11" s="2">
         <v>416984</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>338251</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="2">
         <v>107703</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <v>181816</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11" s="2">
         <v>32074</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>16010</v>
       </c>
-      <c r="I11" s="2">
-        <v>29421</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1628162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2">
+        <v>1689237</v>
+      </c>
+      <c r="C12" s="2">
         <v>522032</v>
       </c>
-      <c r="C12" s="2">
+      <c r="D12" s="2">
         <v>425558</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>358804</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="2">
         <v>116382</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>185879</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <v>36245</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>15780</v>
       </c>
-      <c r="I12" s="2">
-        <v>28191</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1689237</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2">
+        <v>1533427</v>
+      </c>
+      <c r="C13" s="2">
         <v>471157</v>
       </c>
-      <c r="C13" s="2">
+      <c r="D13" s="2">
         <v>385869</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>320209</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="2">
         <v>112543</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>169990</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <v>35758</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>13894</v>
       </c>
-      <c r="I13" s="2">
-        <v>23664</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1533427</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
+        <v>1533966</v>
+      </c>
+      <c r="C14" s="2">
         <v>484474</v>
       </c>
-      <c r="C14" s="2">
+      <c r="D14" s="2">
         <v>376207</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>319683</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="2">
         <v>116081</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>163802</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <v>39529</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>12104</v>
       </c>
-      <c r="I14" s="2">
-        <v>21688</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1533966</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="2">
+        <v>1359091</v>
+      </c>
+      <c r="C15" s="2">
         <v>430532</v>
       </c>
-      <c r="C15" s="2">
+      <c r="D15" s="2">
         <v>335138</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>279929</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="2">
         <v>106010</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="2">
         <v>142860</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <v>36412</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <v>9327</v>
       </c>
-      <c r="I15" s="2">
-        <v>18509</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1359091</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2">
+        <v>1174210</v>
+      </c>
+      <c r="C16" s="2">
         <v>371036</v>
       </c>
-      <c r="C16" s="2">
+      <c r="D16" s="2">
         <v>287351</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>244048</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="2">
         <v>94469</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="2">
         <v>121142</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16" s="2">
         <v>32285</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>6841</v>
       </c>
-      <c r="I16" s="2">
-        <v>16727</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1174210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="2">
+        <v>972111</v>
+      </c>
+      <c r="C17" s="2">
         <v>309256</v>
       </c>
-      <c r="C17" s="2">
+      <c r="D17" s="2">
         <v>237883</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="2">
         <v>202447</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="2">
         <v>79627</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <v>97708</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <v>26339</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>4477</v>
       </c>
-      <c r="I17" s="2">
-        <v>14186</v>
-      </c>
-      <c r="J17" s="2">
-        <v>972111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="2">
+        <v>611366</v>
+      </c>
+      <c r="C18" s="2">
         <v>197365</v>
       </c>
-      <c r="C18" s="2">
+      <c r="D18" s="2">
         <v>152833</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="2">
         <v>123125</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>49883</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>60665</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>16331</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>2415</v>
       </c>
-      <c r="I18" s="2">
-        <v>8629</v>
-      </c>
-      <c r="J18" s="2">
-        <v>611366</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="2">
+        <v>362106</v>
+      </c>
+      <c r="C19" s="2">
         <v>119423</v>
       </c>
-      <c r="C19" s="2">
+      <c r="D19" s="2">
         <v>93387</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="2">
         <v>67666</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="2">
         <v>30388</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <v>36070</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="2">
         <v>9155</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>975</v>
       </c>
-      <c r="I19" s="2">
-        <v>4974</v>
-      </c>
-      <c r="J19" s="2">
-        <v>362106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="2">
+        <v>163422</v>
+      </c>
+      <c r="C20" s="2">
         <v>54619</v>
       </c>
-      <c r="C20" s="2">
+      <c r="D20" s="2">
         <v>43064</v>
       </c>
-      <c r="D20" s="2">
+      <c r="E20" s="2">
         <v>29119</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="2">
         <v>14258</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <v>15780</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <v>3933</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>372</v>
       </c>
-      <c r="I20" s="2">
-        <v>2245</v>
-      </c>
-      <c r="J20" s="2">
-        <v>163422</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="2">
+        <v>48882</v>
+      </c>
+      <c r="C21" s="2">
         <v>16464</v>
       </c>
-      <c r="C21" s="2">
+      <c r="D21" s="2">
         <v>13036</v>
       </c>
-      <c r="D21" s="2">
+      <c r="E21" s="2">
         <v>8580</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="2">
         <v>4525</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>4565</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="2">
         <v>1019</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <v>112</v>
       </c>
-      <c r="I21" s="2">
-        <v>579</v>
-      </c>
-      <c r="J21" s="2">
-        <v>48882</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="2">
+        <v>6363</v>
+      </c>
+      <c r="C22" s="2">
         <v>2194</v>
       </c>
-      <c r="C22" s="2">
+      <c r="D22" s="2">
         <v>1575</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="2">
         <v>1094</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="2">
         <v>610</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <v>653</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <v>115</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>24</v>
       </c>
-      <c r="I22" s="2">
-        <v>97</v>
-      </c>
-      <c r="J22" s="2">
-        <v>6363</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/age_distribution_tidy.xlsx
+++ b/age_distribution_tidy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{8CE5358A-9DD3-4435-A49F-073DC7751DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB65F81-F5C5-4992-9078-2D46B7DAA520}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{8CE5358A-9DD3-4435-A49F-073DC7751DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{839FD28A-8B04-4ED9-AE1A-BC330B2DCED4}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{36764642-B66D-4662-97D4-AD47A217EAF5}"/>
+    <workbookView xWindow="3276" yWindow="2112" windowWidth="17280" windowHeight="8880" xr2:uid="{36764642-B66D-4662-97D4-AD47A217EAF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
     <t>95–99</t>
   </si>
   <si>
-    <t>100 and over</t>
-  </si>
-  <si>
     <t>Age group (years)</t>
   </si>
   <si>
@@ -147,6 +144,9 @@
   </si>
   <si>
     <t>Australia</t>
+  </si>
+  <si>
+    <t>100+</t>
   </si>
 </sst>
 </file>
@@ -565,31 +565,31 @@
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2">
         <v>6363</v>

--- a/age_distribution_tidy.xlsx
+++ b/age_distribution_tidy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{8CE5358A-9DD3-4435-A49F-073DC7751DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{839FD28A-8B04-4ED9-AE1A-BC330B2DCED4}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{8CE5358A-9DD3-4435-A49F-073DC7751DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91C8C0C-D7AB-4EA9-89E9-B88E53F98ACB}"/>
   <bookViews>
-    <workbookView xWindow="3276" yWindow="2112" windowWidth="17280" windowHeight="8880" xr2:uid="{36764642-B66D-4662-97D4-AD47A217EAF5}"/>
+    <workbookView xWindow="3972" yWindow="2808" windowWidth="17280" windowHeight="8880" xr2:uid="{36764642-B66D-4662-97D4-AD47A217EAF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -235,6 +235,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F791B93-A272-4460-B77A-39D571EEC61D}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -561,6 +562,7 @@
     <col min="7" max="7" width="17.33203125" customWidth="1"/>
     <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="17.5546875" customWidth="1"/>
+    <col min="15" max="15" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1029,7 +1031,7 @@
         <v>6841</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1058,7 +1060,7 @@
         <v>4477</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1086,8 +1088,9 @@
       <c r="I18" s="2">
         <v>2415</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1116,7 +1119,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1145,7 +1148,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1174,7 +1177,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -1202,6 +1205,9 @@
       <c r="I22" s="2">
         <v>24</v>
       </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B23" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/age_distribution_tidy.xlsx
+++ b/age_distribution_tidy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{8CE5358A-9DD3-4435-A49F-073DC7751DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91C8C0C-D7AB-4EA9-89E9-B88E53F98ACB}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{8CE5358A-9DD3-4435-A49F-073DC7751DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{155CBDE9-7B62-4156-B335-BC7BD00C15C3}"/>
   <bookViews>
-    <workbookView xWindow="3972" yWindow="2808" windowWidth="17280" windowHeight="8880" xr2:uid="{36764642-B66D-4662-97D4-AD47A217EAF5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{36764642-B66D-4662-97D4-AD47A217EAF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>0–4</t>
   </si>
@@ -147,13 +147,16 @@
   </si>
   <si>
     <t>100+</t>
+  </si>
+  <si>
+    <t>Australian Capital Territory</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,6 +201,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -219,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -236,6 +246,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,7 +565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F791B93-A272-4460-B77A-39D571EEC61D}">
   <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" customWidth="1"/>
@@ -562,6 +576,7 @@
     <col min="7" max="7" width="17.33203125" customWidth="1"/>
     <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="17.5546875" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="8" customWidth="1"/>
     <col min="15" max="15" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -593,10 +608,12 @@
       <c r="I1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="5"/>
+      <c r="J1" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,8 +641,11 @@
       <c r="I2" s="2">
         <v>17434</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J2" s="2">
+        <v>13350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -653,8 +673,11 @@
       <c r="I3" s="2">
         <v>18086</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J3" s="2">
+        <v>14494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -682,8 +705,11 @@
       <c r="I4" s="2">
         <v>17682</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J4" s="2">
+        <v>14704</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -711,8 +737,11 @@
       <c r="I5" s="2">
         <v>15916</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J5" s="2">
+        <v>14697</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -740,8 +769,11 @@
       <c r="I6" s="2">
         <v>18555</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J6" s="2">
+        <v>19672</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -769,8 +801,11 @@
       <c r="I7" s="2">
         <v>23913</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J7" s="2">
+        <v>20545</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -798,8 +833,11 @@
       <c r="I8" s="2">
         <v>25539</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J8" s="2">
+        <v>21083</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -827,8 +865,11 @@
       <c r="I9" s="2">
         <v>22397</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J9" s="2">
+        <v>19060</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,8 +897,11 @@
       <c r="I10" s="2">
         <v>18994</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J10" s="2">
+        <v>17620</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,8 +929,11 @@
       <c r="I11" s="2">
         <v>16010</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J11" s="2">
+        <v>14689</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -914,8 +961,11 @@
       <c r="I12" s="2">
         <v>15780</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J12" s="2">
+        <v>13914</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -943,8 +993,11 @@
       <c r="I13" s="2">
         <v>13894</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J13" s="2">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -972,8 +1025,11 @@
       <c r="I14" s="2">
         <v>12104</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J14" s="2">
+        <v>10411</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1001,8 +1057,11 @@
       <c r="I15" s="2">
         <v>9327</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J15" s="2">
+        <v>8520</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1030,8 +1089,11 @@
       <c r="I16" s="2">
         <v>6841</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J16" s="2">
+        <v>7626</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1059,8 +1121,11 @@
       <c r="I17" s="2">
         <v>4477</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J17" s="2">
+        <v>6531</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1088,9 +1153,12 @@
       <c r="I18" s="2">
         <v>2415</v>
       </c>
+      <c r="J18" s="2">
+        <v>3817</v>
+      </c>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1118,8 +1186,11 @@
       <c r="I19" s="2">
         <v>975</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J19" s="2">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1147,8 +1218,11 @@
       <c r="I20" s="2">
         <v>372</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J20" s="2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1176,8 +1250,11 @@
       <c r="I21" s="2">
         <v>112</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J21" s="2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -1204,6 +1281,9 @@
       </c>
       <c r="I22" s="2">
         <v>24</v>
+      </c>
+      <c r="J22" s="2">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
